--- a/outputs/evaluation/architecture/validation/CF_M06/run_1/CF_M06_arch_eval_llm_report.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M06/run_1/CF_M06_arch_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,145 +481,197 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_18</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>AU_16</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Push Notification Service</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Via sockets es poden rebre els logs en temps real</t>
+          <t>Service responsible for delivering push notifications to devices.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>AU_03, AU_02</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>presentation layer, waapiti server</t>
-        </is>
-      </c>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CF_M06_AU30</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>CF_M06_AU21</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Apple Push Notification Service</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>This functionality connects via socket [25] with the server and displays</t>
+          <t>Firebase Cloud Messaging (FCM) for Android devices and Apple Push Notification Service (APNS) for iOS devices.</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.7084</v>
+        <v>0.9303</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_19</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>AU_20</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Aquesta última pestanya mostra un historial de reproducció del player. A més, es connecta també via socket amb el servidor i mostra logs en temps real.</t>
+          <t>Third-party companies that offer digital signage service/consulting using Waapiti technology.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>AU_03, AU_02</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>presentation layer, waapiti server</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CF_M06_AU30</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>CF_M06_AU08</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>This functionality connects via socket [25] with the server and displays</t>
+          <t xml:space="preserve"> is a Javascript object that indicates an intention to modify the state of the application.</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.7385</v>
+        <v>0.748</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P_01</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>3-Layer Architecture</t>
-        </is>
-      </c>
+          <t>AU_24</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>This architecture follows the 3-layer model: Presentation, Domain, and Data.</t>
+          <t>The application uses sockets to receive logs in real time from the server.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+          <t>38,79</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>AU_03, AU_02</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>presentation layer, waapiti server</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CF_M06_P01</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Three Layers</t>
-        </is>
-      </c>
+          <t>CF_M06_AU30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>This architecture follows the 3-layer model</t>
+          <t>This functionality connects via socket [25] with the server and displays</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.8511</v>
+        <v>0.7722</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AU_26</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>The Push Notification Service delivers push notifications to devices using AWS SNS, Firebase Cloud Messaging, and Apple Push Notification Service.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>AU_16, AU_01, AU_17, AU_18, AU_19</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>push notification service, mobile device, aws sns, firebase cloud messaging, apple push notification service</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>CF_M06_AU21</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Apple Push Notification Service</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Firebase Cloud Messaging (FCM) for Android devices and Apple Push Notification Service (APNS) for iOS devices.</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.8616</v>
       </c>
     </row>
   </sheetData>
